--- a/AAII_Financials/Yearly/AMCR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AMCR_YR_FIN.xlsx
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23506000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15009000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13640000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14694000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14544000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12861000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12468000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9458000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9319100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9101000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9421300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9611800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9964500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9485800</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>18816000</v>
+      </c>
+      <c r="E9" s="3">
         <v>12175000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10928000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11969000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11724000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10129000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9932000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7659000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7462300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7189200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7426500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7679600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8082600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7737800</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4690000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2834000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2712000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2725000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2820000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2732000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2536000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1799000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1856800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1911800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1994800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1932200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1881900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1748000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,53 +888,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>170000</v>
+      </c>
+      <c r="E12" s="3">
         <v>120000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>106000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>101000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>96000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>100000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>97000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>64000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>72700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>137900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>67400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>62900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>69700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>66000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -965,86 +981,92 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>289000</v>
+        <v>250000</v>
       </c>
       <c r="E14" s="3">
-        <v>35000</v>
+        <v>281000</v>
       </c>
       <c r="F14" s="3">
+        <v>44000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-130000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>219000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>95000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>117000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>313000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>41400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>271200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>499000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-8600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>558000</v>
+      </c>
+      <c r="E15" s="3">
         <v>246000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>167000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>160000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>582000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>564000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>630000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>378000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>352700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36200</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>11</v>
@@ -1055,9 +1077,12 @@
       <c r="P15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13694000</v>
+        <v>21390000</v>
       </c>
       <c r="E17" s="3">
-        <v>12366000</v>
+        <v>13647000</v>
       </c>
       <c r="F17" s="3">
+        <v>12357000</v>
+      </c>
+      <c r="G17" s="3">
         <v>13306000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13037000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11425000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11365000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8360000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8276200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8184900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8845600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8546700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8882400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8504700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1315000</v>
+        <v>2116000</v>
       </c>
       <c r="E18" s="3">
-        <v>1274000</v>
+        <v>1362000</v>
       </c>
       <c r="F18" s="3">
+        <v>1283000</v>
+      </c>
+      <c r="G18" s="3">
         <v>1388000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1507000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1436000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1103000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1098000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1042900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>916100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>575700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1065100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1082100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>981100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>26000</v>
+        <v>-31000</v>
       </c>
       <c r="E20" s="3">
+        <v>81000</v>
+      </c>
+      <c r="F20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>24000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>38000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>99200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>180700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>17200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1535000</v>
+        <v>2705000</v>
       </c>
       <c r="E21" s="3">
-        <v>1431000</v>
+        <v>1527000</v>
       </c>
       <c r="F21" s="3">
+        <v>1440000</v>
+      </c>
+      <c r="G21" s="3">
         <v>1524000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2051000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2014000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1743000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1490000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1296400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1471000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>991200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1459100</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>676000</v>
+      </c>
+      <c r="E22" s="3">
         <v>396000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>364000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>274000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>159000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>157000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>207000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>208000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>210000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>381000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>192200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>186400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>208400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>156100</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1287000</v>
+      </c>
+      <c r="E23" s="3">
         <v>653000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>903000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1251000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1115000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1212000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>811000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>608000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>705400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>715800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>408900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>895900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>888900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>790000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E24" s="3">
         <v>135000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>163000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>193000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>261000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>187000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>172000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>118800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>148900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>135300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>188000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>182200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>173000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="E26" s="3">
         <v>518000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>740000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1058000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>815000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>951000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>624000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>436000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>586600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>566900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>273600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>707900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>706700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>617000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="E27" s="3">
         <v>510000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>727000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1041000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>802000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>937000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>612000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>429000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>573900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>564000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>244100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>680300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>677800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>589200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1607,32 +1667,35 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-8000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-174900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-26000</v>
+        <v>31000</v>
       </c>
       <c r="E32" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-24000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-38000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-99200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-180700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-17200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>35000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="E33" s="3">
         <v>511000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>730000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1048000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>805000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>939000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>612000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>430000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>575200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>564000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>244100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>680300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>502900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>583700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="E35" s="3">
         <v>511000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>730000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1048000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>805000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>939000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>612000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>430000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>575200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>564000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>244100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>680300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>502900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>583700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2074,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1115000</v>
+      </c>
+      <c r="E41" s="3">
         <v>827000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>588000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>689000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>775000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>850000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>743000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>601600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>620800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>447800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>420500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>596300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>899800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>658200</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2046,17 +2135,17 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>16000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>15000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2064,338 +2153,362 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>113700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>95200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>108600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>238800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>102700</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3639000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3426000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1846000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1875000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1935000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1864000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1616000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1864300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1379000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1328000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1339300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1385700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2963900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3610500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3672000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3471000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2031000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2213000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2439000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1991000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1832000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1953800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1358800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1305500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1244400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1213900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2658000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3496800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E45" s="3">
         <v>7000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>202000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>421200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>91500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>93700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>108500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>114400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>220400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9326000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8434000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4965000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5308000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5853000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5266000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4535000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5210100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3620300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3286500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3193100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3413000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3326500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3891100</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E47" s="3">
         <v>100000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>87000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>89000</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>110000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>131700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>138600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>411900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>446500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>458200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>595100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>578700</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8448000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9318000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4330000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4295000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4206000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4293000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4140000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3975000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2698500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2765300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2690900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2566700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5840200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4763000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18663000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18679000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6736000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6890000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6942000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7254000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7333000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7462800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2381400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2409300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2102100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1845300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3992600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4180400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E52" s="3">
         <v>317000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>258000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>287000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>295000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>232000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>189000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>194500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>148000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>210300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>249500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>263900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>580200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>715400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37095000</v>
+      </c>
+      <c r="E54" s="3">
         <v>37066000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16524000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17003000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17426000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17188000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16442000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17165000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9057500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9083300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8682100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8547100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9133900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11515600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4021000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3490000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2580000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2690000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3073000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2574000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2171000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2303400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1861000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2607900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2418400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2345700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5133500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5949100</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>366000</v>
+      </c>
+      <c r="E58" s="3">
         <v>497000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>210000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>194000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>251000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>199000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>290000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>794200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2157900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1124600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>916700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1012700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1490700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3558000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2343000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2369000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1061000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1190000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1301000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1041000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1024000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1058400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>760200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>301700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>310100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>316000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>482400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>783700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7435000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6987000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4261000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4476000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5103000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4345000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3974000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4541800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5055200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4034200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3645200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3674400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3296000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4358600</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14774000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14814000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7183000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7212000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6902000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6648000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6494000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5309000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2691700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3486400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3428400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2572600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3001300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2945700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>696000</v>
+      </c>
+      <c r="E62" s="3">
         <v>691000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>326000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>385000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>402000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>371000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>223000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>241000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>181400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>693000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>763000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>713100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>837000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>994300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25294000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25326000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12571000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12913000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13285000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12367000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11755000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11490300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8362100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8283200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7898200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7080900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7105800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8171000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>459000</v>
+      </c>
+      <c r="E72" s="3">
         <v>548000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>879000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>865000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>534000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>452000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>246000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>323700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>561400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-334100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-458900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-141600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-635500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>669500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11790000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11728000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3881000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4026000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4082000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4764000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4626000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5609000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>626600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>800100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>783900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1466200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2028100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3344600</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1106000</v>
+      </c>
+      <c r="E81" s="3">
         <v>511000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>730000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1048000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>805000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>939000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>612000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>430000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>575200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>564000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>244100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>680300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>502900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>583700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>722000</v>
+        <v>843000</v>
       </c>
       <c r="E83" s="3">
-        <v>595000</v>
+        <v>451000</v>
       </c>
       <c r="F83" s="3">
+        <v>402000</v>
+      </c>
+      <c r="G83" s="3">
         <v>586000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>402000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>382000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>426000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>334000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>320800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>374200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>390100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>376800</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2151000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1390000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1321000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1261000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1526000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1461000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1384000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>776000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>871400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>908900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1099400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1002300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1094100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1046500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-922000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-580000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-492000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-526000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-527000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-468000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-332000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-365000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-758500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-348900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-323000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-332600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-323400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-524000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2102000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-476000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-309000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-527000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-233000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>38000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-241900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-632000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-997000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-335300</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1195000</v>
+      </c>
+      <c r="E96" s="3">
         <v>842000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>716000</v>
       </c>
       <c r="F96" s="3">
         <v>716000</v>
       </c>
       <c r="G96" s="3">
+        <v>716000</v>
+      </c>
+      <c r="H96" s="3">
         <v>723000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>728000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>748000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>666000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>515500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-489100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-480300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-480100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-460200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-478200</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1343000</v>
+      </c>
+      <c r="E100" s="3">
         <v>910000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-857000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1025000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-891000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1179000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-765000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-542700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-223000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-126900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-473300</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>41000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-89000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-88000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-108000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>58000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-45000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-27500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-159600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1400</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>288000</v>
+      </c>
+      <c r="E102" s="3">
         <v>239000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-101000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-161000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>107000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>141000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>59300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>45800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-184100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>192300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>165500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>44400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
